--- a/แม่แบบชีตใหม่/ชีตแม่แบบ-ระบบติดตามมาตรฐานโรงพยาบาล.xlsx
+++ b/แม่แบบชีตใหม่/ชีตแม่แบบ-ระบบติดตามมาตรฐานโรงพยาบาล.xlsx
@@ -106,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,6 +123,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2449,7 +2452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N499"/>
+  <dimension ref="A1:O499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2466,6 +2469,7 @@
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -2536,7 +2540,12 @@
       </c>
       <c r="N1" s="3" t="inlineStr">
         <is>
-          <t>ระดับผลการประเมิน</t>
+          <t>ระดับที่ส่งการประเมิน Green</t>
+        </is>
+      </c>
+      <c r="O1" s="8" t="inlineStr">
+        <is>
+          <t>รับรองผลการประเมิน</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N499"/>
+  <dimension ref="A1:O499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4063,6 +4072,7 @@
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -4133,7 +4143,12 @@
       </c>
       <c r="N1" s="3" t="inlineStr">
         <is>
-          <t>ระดับผลการประเมิน</t>
+          <t>ระดับที่ส่งประเมิน อาชีวฯ</t>
+        </is>
+      </c>
+      <c r="O1" s="8" t="inlineStr">
+        <is>
+          <t>รับรองผลการประเมิน</t>
         </is>
       </c>
     </row>
